--- a/data/trans_dic/Q23_tabaco_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,09; 44,93</t>
+          <t>28,16; 45,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,37; 47,77</t>
+          <t>32,39; 47,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,66; 59,44</t>
+          <t>44,22; 59,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,14; 54,99</t>
+          <t>35,75; 57,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,79; 36,92</t>
+          <t>15,88; 36,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,58; 43,42</t>
+          <t>23,41; 42,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,56; 44,0</t>
+          <t>25,74; 43,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,87; 29,36</t>
+          <t>14,32; 29,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,61; 39,47</t>
+          <t>25,25; 38,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,31; 43,13</t>
+          <t>31,38; 42,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,68; 50,64</t>
+          <t>38,41; 50,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 42,98</t>
+          <t>29,32; 44,55</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,24; 48,84</t>
+          <t>35,4; 47,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,05; 48,67</t>
+          <t>37,48; 49,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 38,3</t>
+          <t>26,32; 37,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 41,97</t>
+          <t>25,51; 40,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,95; 35,93</t>
+          <t>21,15; 36,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,21; 38,13</t>
+          <t>24,75; 38,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 34,6</t>
+          <t>20,47; 34,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 33,64</t>
+          <t>21,35; 33,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,99; 41,72</t>
+          <t>32,08; 42,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,95; 42,93</t>
+          <t>33,99; 42,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,03; 34,54</t>
+          <t>25,73; 34,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,0; 36,04</t>
+          <t>25,57; 35,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,64; 47,72</t>
+          <t>32,96; 47,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,29; 41,93</t>
+          <t>28,48; 42,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,24; 39,26</t>
+          <t>24,73; 39,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,17; 57,97</t>
+          <t>41,99; 57,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 35,11</t>
+          <t>18,28; 35,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 34,29</t>
+          <t>17,24; 35,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,03; 37,07</t>
+          <t>20,16; 37,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 31,39</t>
+          <t>17,5; 31,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 40,47</t>
+          <t>28,97; 40,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 36,85</t>
+          <t>26,1; 37,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,98; 35,58</t>
+          <t>24,56; 35,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,87; 43,85</t>
+          <t>33,02; 43,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,38; 37,48</t>
+          <t>24,65; 37,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,29; 41,5</t>
+          <t>27,41; 41,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,26; 47,47</t>
+          <t>34,04; 47,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 30,37</t>
+          <t>17,51; 30,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 28,02</t>
+          <t>14,61; 27,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 25,19</t>
+          <t>11,76; 25,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 34,91</t>
+          <t>20,31; 35,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 31,38</t>
+          <t>16,36; 31,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,03; 31,53</t>
+          <t>21,9; 31,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,31; 32,62</t>
+          <t>22,34; 32,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,09; 40,12</t>
+          <t>30,3; 40,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 28,37</t>
+          <t>18,3; 28,31</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 31,19</t>
+          <t>14,82; 31,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,3; 49,96</t>
+          <t>31,58; 49,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,87; 40,87</t>
+          <t>24,48; 41,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 33,84</t>
+          <t>16,59; 35,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,59; 40,45</t>
+          <t>19,54; 40,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,78; 43,2</t>
+          <t>23,22; 43,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 38,6</t>
+          <t>18,69; 38,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,39; 37,56</t>
+          <t>17,34; 36,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 32,46</t>
+          <t>19,01; 31,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,24; 45,19</t>
+          <t>31,3; 44,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,78; 37,64</t>
+          <t>24,39; 37,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 32,55</t>
+          <t>19,03; 32,85</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,93; 48,29</t>
+          <t>32,25; 48,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,31; 44,53</t>
+          <t>29,65; 44,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,2; 37,01</t>
+          <t>20,85; 36,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,95; 50,68</t>
+          <t>34,41; 49,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,51; 40,64</t>
+          <t>20,3; 40,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,67; 39,68</t>
+          <t>20,78; 40,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 22,97</t>
+          <t>7,74; 22,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,05; 41,39</t>
+          <t>21,62; 41,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,06; 44,14</t>
+          <t>29,95; 43,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,49; 40,97</t>
+          <t>28,94; 41,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,11; 28,31</t>
+          <t>17,22; 28,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,87; 44,46</t>
+          <t>32,57; 44,64</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,04; 40,99</t>
+          <t>29,72; 41,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,62; 40,74</t>
+          <t>31,04; 40,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,73; 39,12</t>
+          <t>27,32; 38,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,8; 43,87</t>
+          <t>31,3; 44,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,05; 34,46</t>
+          <t>21,97; 34,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,8; 34,27</t>
+          <t>22,82; 34,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,19; 29,19</t>
+          <t>18,39; 29,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,97; 34,34</t>
+          <t>23,2; 34,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,8; 36,75</t>
+          <t>27,93; 36,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,38; 36,57</t>
+          <t>29,1; 36,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,8; 32,76</t>
+          <t>24,83; 32,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,26; 37,91</t>
+          <t>28,81; 38,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,86; 37,36</t>
+          <t>28,42; 37,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,19; 32,89</t>
+          <t>23,47; 32,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,25; 43,04</t>
+          <t>32,66; 43,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 25,97</t>
+          <t>3,79; 25,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,77; 31,85</t>
+          <t>20,09; 31,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,79; 32,07</t>
+          <t>20,61; 32,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,23; 32,11</t>
+          <t>20,87; 32,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,15; 20,4</t>
+          <t>10,22; 20,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,21; 33,9</t>
+          <t>26,24; 33,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,61; 30,93</t>
+          <t>23,6; 30,81</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,14; 36,56</t>
+          <t>28,89; 36,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,67; 22,12</t>
+          <t>4,86; 21,92</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,03; 37,64</t>
+          <t>33,25; 37,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33,61; 37,95</t>
+          <t>33,75; 38,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,85; 38,42</t>
+          <t>33,83; 38,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,86; 34,95</t>
+          <t>17,78; 35,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,71; 29,28</t>
+          <t>23,53; 29,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,13; 30,47</t>
+          <t>25,15; 30,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,54; 28,6</t>
+          <t>23,4; 28,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,81; 26,61</t>
+          <t>21,64; 26,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,04; 33,72</t>
+          <t>30,17; 33,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,83; 34,21</t>
+          <t>30,97; 34,39</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29,97; 33,66</t>
+          <t>30,03; 33,63</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,82; 30,86</t>
+          <t>19,29; 30,68</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38592; 59605</t>
+          <t>37360; 59863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58930; 86974</t>
+          <t>58966; 86133</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76804; 104569</t>
+          <t>77788; 104249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46347; 72532</t>
+          <t>47152; 75543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12163; 28439</t>
+          <t>12234; 28238</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31164; 55049</t>
+          <t>29672; 54377</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33592; 55650</t>
+          <t>32561; 55598</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11469; 22645</t>
+          <t>11042; 22373</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53690; 82762</t>
+          <t>52936; 80546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96701; 133195</t>
+          <t>96910; 131724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116982; 153160</t>
+          <t>116170; 152741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60846; 89826</t>
+          <t>61287; 93119</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93445; 129514</t>
+          <t>93861; 125965</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>119485; 156948</t>
+          <t>120846; 159226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75782; 107783</t>
+          <t>74084; 106311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64143; 102828</t>
+          <t>62499; 99601</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27998; 48020</t>
+          <t>28266; 48862</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49606; 78126</t>
+          <t>50712; 78017</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35668; 60435</t>
+          <t>35748; 59626</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33591; 55240</t>
+          <t>35048; 54296</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127572; 166383</t>
+          <t>127943; 168473</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179027; 226408</t>
+          <t>179235; 226377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>118707; 157540</t>
+          <t>117351; 158554</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>106382; 147490</t>
+          <t>104635; 146072</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55675; 81395</t>
+          <t>56221; 80760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59124; 87624</t>
+          <t>59508; 87785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37753; 61160</t>
+          <t>38520; 61650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58713; 80705</t>
+          <t>58454; 79500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18291; 34920</t>
+          <t>18182; 35233</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20714; 41053</t>
+          <t>20634; 42497</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21105; 39049</t>
+          <t>21240; 39490</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19128; 34560</t>
+          <t>19270; 34692</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78877; 109288</t>
+          <t>78217; 109965</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86458; 121135</t>
+          <t>85798; 121759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65220; 92910</t>
+          <t>64138; 92539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81957; 109320</t>
+          <t>82320; 108846</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49721; 76429</t>
+          <t>50275; 76992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57436; 87345</t>
+          <t>57684; 86886</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79715; 110450</t>
+          <t>79199; 109806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28522; 51001</t>
+          <t>29405; 51594</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18816; 36531</t>
+          <t>19047; 36306</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17215; 36934</t>
+          <t>17244; 36793</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31677; 54624</t>
+          <t>31787; 54799</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21257; 40281</t>
+          <t>21009; 39795</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73651; 105402</t>
+          <t>73216; 105375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79670; 116483</t>
+          <t>79783; 116713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117109; 156120</t>
+          <t>117918; 156615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54516; 84051</t>
+          <t>54221; 83879</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15311; 32334</t>
+          <t>15364; 32446</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44863; 69397</t>
+          <t>43873; 68274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27632; 47313</t>
+          <t>28335; 48163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7879; 16439</t>
+          <t>8059; 17163</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13855; 30148</t>
+          <t>14563; 30159</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21946; 39869</t>
+          <t>21430; 40254</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13319; 27794</t>
+          <t>13461; 27769</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6641; 14342</t>
+          <t>6622; 13911</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33848; 57855</t>
+          <t>33882; 56974</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72225; 104488</t>
+          <t>72356; 103022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44649; 70678</t>
+          <t>45788; 70715</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16349; 28243</t>
+          <t>16508; 28496</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51410; 75405</t>
+          <t>50351; 75487</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48347; 73451</t>
+          <t>48907; 73591</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28367; 49533</t>
+          <t>27906; 48889</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42089; 61044</t>
+          <t>41443; 59651</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15771; 31240</t>
+          <t>15608; 31037</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17797; 34166</t>
+          <t>17895; 34885</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7078; 20223</t>
+          <t>6817; 19519</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13031; 24460</t>
+          <t>12777; 24559</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72383; 102859</t>
+          <t>69777; 100677</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71536; 102856</t>
+          <t>72654; 103831</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37968; 62806</t>
+          <t>38207; 63784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57224; 79825</t>
+          <t>58483; 80155</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>89819; 122573</t>
+          <t>88862; 124712</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>127527; 169690</t>
+          <t>129308; 169785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86810; 122447</t>
+          <t>85536; 120971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89829; 127971</t>
+          <t>91288; 128999</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39242; 64230</t>
+          <t>40955; 64480</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62108; 93343</t>
+          <t>62155; 93216</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45304; 72713</t>
+          <t>45802; 72751</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56268; 84138</t>
+          <t>56839; 84453</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>139799; 178379</t>
+          <t>135588; 178608</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>202391; 251905</t>
+          <t>200437; 251746</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>139435; 184178</t>
+          <t>139598; 182699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>157027; 203460</t>
+          <t>154638; 204642</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>108624; 145679</t>
+          <t>110816; 146304</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>96762; 131555</t>
+          <t>93889; 131113</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>116217; 155119</t>
+          <t>117711; 157424</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18782; 136286</t>
+          <t>19881; 135273</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43494; 70076</t>
+          <t>44198; 68954</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55851; 86144</t>
+          <t>55360; 86685</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57822; 87447</t>
+          <t>56847; 87513</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15396; 30942</t>
+          <t>15492; 31375</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>159898; 206758</t>
+          <t>160066; 206850</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>157830; 206773</t>
+          <t>157793; 206034</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184368; 231315</t>
+          <t>182814; 230841</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>31617; 149666</t>
+          <t>32895; 148285</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>568525; 647867</t>
+          <t>572225; 650850</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>687193; 775790</t>
+          <t>689918; 780342</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>598752; 679504</t>
+          <t>598347; 681670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>298145; 583493</t>
+          <t>296898; 587979</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>236687; 292305</t>
+          <t>234941; 292311</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>331091; 401390</t>
+          <t>331337; 402629</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>292931; 355893</t>
+          <t>291263; 356031</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>212404; 259085</t>
+          <t>210736; 259962</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>816937; 916984</t>
+          <t>820550; 919160</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1036339; 1150041</t>
+          <t>1041138; 1156243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>903152; 1014274</t>
+          <t>904954; 1013420</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>523840; 815602</t>
+          <t>509845; 811062</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q23_tabaco_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,16; 45,13</t>
+          <t>28,28; 45,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 47,31</t>
+          <t>32,11; 47,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,22; 59,26</t>
+          <t>44,19; 59,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,75; 57,28</t>
+          <t>31,42; 49,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,88; 36,66</t>
+          <t>16,04; 36,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,41; 42,89</t>
+          <t>24,91; 43,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,74; 43,95</t>
+          <t>26,11; 43,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 29,01</t>
+          <t>14,17; 29,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,25; 38,42</t>
+          <t>26,37; 39,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 42,65</t>
+          <t>31,18; 42,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 50,51</t>
+          <t>38,61; 50,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 44,55</t>
+          <t>27,39; 39,61</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,4; 47,5</t>
+          <t>35,44; 48,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,48; 49,38</t>
+          <t>37,19; 48,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,32; 37,77</t>
+          <t>27,0; 38,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,51; 40,65</t>
+          <t>27,67; 41,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,15; 36,56</t>
+          <t>20,51; 35,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,75; 38,08</t>
+          <t>24,83; 38,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,47; 34,14</t>
+          <t>20,71; 34,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,35; 33,07</t>
+          <t>20,92; 33,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,08; 42,24</t>
+          <t>31,81; 41,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,99; 42,93</t>
+          <t>34,26; 43,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,73; 34,76</t>
+          <t>26,32; 35,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,57; 35,7</t>
+          <t>26,45; 35,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,96; 47,34</t>
+          <t>32,6; 47,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,48; 42,01</t>
+          <t>28,26; 42,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,73; 39,58</t>
+          <t>24,33; 38,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,99; 57,11</t>
+          <t>42,14; 57,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 35,43</t>
+          <t>17,58; 34,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 35,5</t>
+          <t>17,82; 34,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 37,49</t>
+          <t>19,55; 36,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 31,51</t>
+          <t>17,74; 30,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,97; 40,72</t>
+          <t>29,07; 40,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 37,04</t>
+          <t>26,89; 37,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,56; 35,44</t>
+          <t>25,3; 36,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,02; 43,66</t>
+          <t>32,97; 44,44</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,65; 37,75</t>
+          <t>24,45; 37,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,41; 41,29</t>
+          <t>27,53; 41,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 47,19</t>
+          <t>33,82; 47,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,51; 30,72</t>
+          <t>17,58; 31,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 27,85</t>
+          <t>13,31; 27,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 25,09</t>
+          <t>11,89; 25,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 35,02</t>
+          <t>19,55; 34,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 31,0</t>
+          <t>15,9; 30,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 31,52</t>
+          <t>21,99; 31,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,34; 32,69</t>
+          <t>22,96; 32,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,3; 40,24</t>
+          <t>30,23; 39,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 28,31</t>
+          <t>18,56; 28,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 31,3</t>
+          <t>15,35; 30,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,58; 49,15</t>
+          <t>32,29; 49,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,48; 41,61</t>
+          <t>24,2; 40,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,59; 35,33</t>
+          <t>17,1; 35,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,54; 40,46</t>
+          <t>18,54; 40,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,22; 43,62</t>
+          <t>24,12; 43,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,69; 38,56</t>
+          <t>18,72; 38,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 36,43</t>
+          <t>17,58; 37,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,01; 31,97</t>
+          <t>19,16; 32,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,3; 44,56</t>
+          <t>30,81; 43,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,39; 37,66</t>
+          <t>24,07; 37,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 32,85</t>
+          <t>19,08; 32,62</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,25; 48,35</t>
+          <t>33,0; 48,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,65; 44,61</t>
+          <t>29,71; 44,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,85; 36,53</t>
+          <t>21,05; 36,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,41; 49,53</t>
+          <t>33,59; 49,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,3; 40,37</t>
+          <t>20,5; 41,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,78; 40,52</t>
+          <t>20,35; 40,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 22,17</t>
+          <t>7,5; 22,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 41,55</t>
+          <t>21,61; 41,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,95; 43,21</t>
+          <t>30,85; 43,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,94; 41,36</t>
+          <t>28,35; 40,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,22; 28,75</t>
+          <t>17,09; 28,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,57; 44,64</t>
+          <t>32,34; 44,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,72; 41,71</t>
+          <t>30,63; 41,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,04; 40,76</t>
+          <t>31,16; 40,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,32; 38,64</t>
+          <t>27,51; 39,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,3; 44,23</t>
+          <t>30,91; 42,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,97; 34,6</t>
+          <t>21,84; 34,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,82; 34,22</t>
+          <t>23,25; 34,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,39; 29,21</t>
+          <t>18,36; 29,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,2; 34,47</t>
+          <t>21,17; 31,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,93; 36,8</t>
+          <t>28,05; 36,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,1; 36,54</t>
+          <t>28,99; 36,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,83; 32,5</t>
+          <t>24,81; 32,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,81; 38,13</t>
+          <t>27,86; 35,57</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,42; 37,52</t>
+          <t>27,86; 37,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,47; 32,78</t>
+          <t>24,06; 33,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,66; 43,68</t>
+          <t>32,62; 43,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 25,77</t>
+          <t>19,49; 28,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,09; 31,34</t>
+          <t>19,75; 32,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,27</t>
+          <t>20,87; 31,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,87; 32,13</t>
+          <t>21,07; 31,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,69</t>
+          <t>10,33; 20,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,24; 33,91</t>
+          <t>26,49; 33,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,6; 30,81</t>
+          <t>23,98; 30,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,89; 36,48</t>
+          <t>28,93; 36,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 21,92</t>
+          <t>17,34; 24,43</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,25; 37,82</t>
+          <t>32,97; 37,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33,75; 38,17</t>
+          <t>33,81; 38,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,83; 38,54</t>
+          <t>33,72; 38,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,78; 35,22</t>
+          <t>31,06; 36,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,28</t>
+          <t>23,52; 29,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,15; 30,56</t>
+          <t>25,16; 30,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,4; 28,61</t>
+          <t>23,78; 28,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,64; 26,7</t>
+          <t>21,14; 25,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,17; 33,8</t>
+          <t>30,22; 33,88</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,97; 34,39</t>
+          <t>31,09; 34,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,03; 33,63</t>
+          <t>30,16; 33,69</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,29; 30,68</t>
+          <t>27,68; 31,11</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>68124</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37360; 59863</t>
+          <t>37513; 60347</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58966; 86133</t>
+          <t>58468; 86771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77788; 104249</t>
+          <t>77748; 103976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47152; 75543</t>
+          <t>39686; 62201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12234; 28238</t>
+          <t>12354; 28488</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29672; 54377</t>
+          <t>31579; 55586</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32561; 55598</t>
+          <t>33027; 54736</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11042; 22373</t>
+          <t>11162; 22930</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52936; 80546</t>
+          <t>55301; 83402</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96910; 131724</t>
+          <t>96289; 132084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116170; 152741</t>
+          <t>116778; 152350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61287; 93119</t>
+          <t>56164; 81242</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81638</t>
+          <t>87977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43710</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>125348</t>
+          <t>132898</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93861; 125965</t>
+          <t>93983; 128079</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>120846; 159226</t>
+          <t>119934; 157154</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74084; 106311</t>
+          <t>75991; 108825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62499; 99601</t>
+          <t>70892; 107239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28266; 48862</t>
+          <t>27416; 48095</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50712; 78017</t>
+          <t>50884; 78519</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35748; 59626</t>
+          <t>36172; 60107</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35048; 54296</t>
+          <t>35332; 55833</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127943; 168473</t>
+          <t>126852; 166356</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179235; 226377</t>
+          <t>180659; 227820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117351; 158554</t>
+          <t>120040; 161079</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104635; 146072</t>
+          <t>112457; 152996</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69658</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>98330</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56221; 80760</t>
+          <t>55603; 81181</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59508; 87785</t>
+          <t>59048; 88086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38520; 61650</t>
+          <t>37898; 59748</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58454; 79500</t>
+          <t>60537; 82071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18182; 35233</t>
+          <t>17484; 34655</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20634; 42497</t>
+          <t>21335; 41666</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21240; 39490</t>
+          <t>20589; 38728</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19270; 34692</t>
+          <t>19669; 33866</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78217; 109965</t>
+          <t>78502; 108893</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85798; 121759</t>
+          <t>88398; 123223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64138; 92539</t>
+          <t>66057; 94170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82320; 108846</t>
+          <t>83914; 113098</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>46464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68016</t>
+          <t>77211</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50275; 76992</t>
+          <t>49868; 76270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57684; 86886</t>
+          <t>57929; 87400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79199; 109806</t>
+          <t>78704; 110619</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29405; 51594</t>
+          <t>34478; 61030</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19047; 36306</t>
+          <t>17357; 35569</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17244; 36793</t>
+          <t>17428; 37394</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31787; 54799</t>
+          <t>30590; 54403</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21009; 39795</t>
+          <t>22530; 42748</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73216; 105375</t>
+          <t>73521; 104625</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79783; 116713</t>
+          <t>81984; 117453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117918; 156615</t>
+          <t>117641; 155306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54221; 83879</t>
+          <t>62696; 95888</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>25136</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15364; 32446</t>
+          <t>15915; 32103</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43873; 68274</t>
+          <t>44858; 68902</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28335; 48163</t>
+          <t>28017; 47229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8059; 17163</t>
+          <t>9718; 20283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14563; 30159</t>
+          <t>13821; 30162</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21430; 40254</t>
+          <t>22257; 39762</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13461; 27769</t>
+          <t>13482; 27894</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6622; 13911</t>
+          <t>7208; 15345</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33882; 56974</t>
+          <t>34138; 57404</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72356; 103022</t>
+          <t>71231; 101005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45788; 70715</t>
+          <t>45199; 69794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16508; 28496</t>
+          <t>18666; 31907</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>50353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68862</t>
+          <t>69044</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50351; 75487</t>
+          <t>51522; 75187</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48907; 73591</t>
+          <t>49005; 73408</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27906; 48889</t>
+          <t>28167; 49422</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41443; 59651</t>
+          <t>40481; 59968</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15608; 31037</t>
+          <t>15758; 31994</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17895; 34885</t>
+          <t>17518; 35048</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6817; 19519</t>
+          <t>6602; 19867</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12777; 24559</t>
+          <t>13051; 25048</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69777; 100677</t>
+          <t>71887; 100782</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72654; 103831</t>
+          <t>71189; 100763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38207; 63784</t>
+          <t>37924; 62251</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58483; 80155</t>
+          <t>58506; 80195</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>121095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>177719</t>
+          <t>194821</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>88862; 124712</t>
+          <t>91578; 125246</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>129308; 169785</t>
+          <t>129790; 169963</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85536; 120971</t>
+          <t>86119; 122784</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91288; 128999</t>
+          <t>101795; 139819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40955; 64480</t>
+          <t>40706; 65092</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62155; 93216</t>
+          <t>63330; 94587</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45802; 72751</t>
+          <t>45721; 72966</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56839; 84453</t>
+          <t>59485; 87825</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>135588; 178608</t>
+          <t>136153; 179368</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>200437; 251746</t>
+          <t>199718; 249739</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>139598; 182699</t>
+          <t>139444; 184726</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>154638; 204642</t>
+          <t>170035; 217110</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68164</t>
+          <t>75542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90607</t>
+          <t>101304</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>110816; 146304</t>
+          <t>108643; 145739</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>93889; 131113</t>
+          <t>96221; 132423</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117711; 157424</t>
+          <t>117571; 154971</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19881; 135273</t>
+          <t>61887; 91761</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44198; 68954</t>
+          <t>43460; 70519</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55360; 86685</t>
+          <t>56061; 84362</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56847; 87513</t>
+          <t>57387; 85440</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15492; 31375</t>
+          <t>17898; 35688</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>160066; 206850</t>
+          <t>161554; 206707</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>157793; 206034</t>
+          <t>160315; 205808</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>182814; 230841</t>
+          <t>183073; 233015</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32895; 148285</t>
+          <t>85074; 119878</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>572225; 650850</t>
+          <t>567441; 653171</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>689918; 780342</t>
+          <t>691164; 779873</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>598347; 681670</t>
+          <t>596422; 678993</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>296898; 587979</t>
+          <t>480345; 557676</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>234941; 292311</t>
+          <t>234847; 290074</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>331337; 402629</t>
+          <t>331478; 400047</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>291263; 356031</t>
+          <t>295955; 357459</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>210736; 259962</t>
+          <t>223224; 273858</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>820550; 919160</t>
+          <t>821881; 921289</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1041138; 1156243</t>
+          <t>1045128; 1159739</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>904954; 1013420</t>
+          <t>908851; 1015207</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>509845; 811062</t>
+          <t>720426; 809577</t>
         </is>
       </c>
     </row>
